--- a/ExcelFiles/SwagLoginTestData.xlsx
+++ b/ExcelFiles/SwagLoginTestData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QT\QT_Selenium_228,229\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51602820-EA5B-4E9C-8640-C91142742749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A57513-D8D5-45A8-A481-111AF1CA36B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="8">
   <si>
     <t>UserName</t>
   </si>
@@ -43,13 +43,19 @@
   </si>
   <si>
     <t>invalisusername</t>
+  </si>
+  <si>
+    <t>invalidpwd</t>
+  </si>
+  <si>
+    <t>abcdefgh</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -61,6 +67,14 @@
       <sz val="8"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -98,10 +112,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -389,10 +404,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
@@ -414,7 +429,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>3</v>
@@ -425,7 +440,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
